--- a/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
+++ b/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지표정의" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면구성" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종목펀더멘털항목" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,4 +881,170 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-macro-fundamentals</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:00:58.926+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S07:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 LLM Wiki와 관련 산출물에 반영하고, 지표 정의·데이터 출처·갱신 SLA·컴플라이언스·공통 데이터 모델·지원 시장 범위는 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>투자 대시보드의 거시경제·개별 종목 펀더멘털 패널 분리와 지표별 갱신 주기 정의를 위한 요구사항 정리를 시작했습니다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/a683884d878122db5364b1930492388be087c398</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-macro-fundamentals</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:04:32.641+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S07:B10000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 투자 대시보드 관련 산출물과 테스트 시나리오에 반영하며, 지표 범위·갱신 기준·출처·라이선스·공통 데이터 모델은 후속 확정한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>거시경제와 개별 종목 펀더멘털 패널을 분리하고 지표 갱신 유형, 기준 시각, 최종 갱신 시각, 데이터 출처, 지연 여부 및 패널별 검증 시나리오를 추가한다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/0323a04300719796cb774e73746a60cc8908d756</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
+++ b/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,56 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-macro-fundamentals</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:08:12.025+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S07:B01000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 관련 기능정의서·정책서·데이터 요구사항·테스트 시나리오와 기성 산출물에 반영하며, 지표 사전·출처·신선도 SLA·공통 데이터 모델·컴플라이언스는 후속 확정한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>투자 대시보드에 거시경제·종목 펀더멘털 패널과 지표 갱신·신선도 표시 요건을 반영했으며, 세부 범위와 출처는 후속 확정이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/fc9da066877ee1a6a8b0ื่อน385cb2e48c20a8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
+++ b/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,6 +1094,56 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-macro-fundamentals</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:11:16.529+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S07:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>승인. 패널 분리, 지표 범위, 갱신 정책, 기준 시각·출처·지연 여부 표시 및 테스트 시나리오를 반영하며, 대상 범위·산식·출처·라이선스·신선도 SLA·공통 데이터 모델은 후속 확정 사항으로 추적한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>투자 대시보드를 거시경제·개별 종목 펀더멘털 패널로 분리하고 갱신 유형 및 데이터 신선도 표시 요구사항을 반영했으며, 세부 주기·출처·산식은 후속 확정입니다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/340f8783721d33a1a5b0cd49c4fb33de55ad29fc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
+++ b/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,6 +1144,56 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-macro-fundamentals-deliverable-update</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:42:05.492+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S07:B00010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 투자 대시보드·데이터·테스트·통합 산출물·추적표·보고 장표에 반영했으며, 대상 범위·산식·데이터 권리·컴플라이언스·공통 모델·SLA는 후속 확정한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>투자 대시보드의 거시경제·개별 종목 펀더멘털 패널 분리와 데이터 갱신·신선도 표시 요구사항을 반영했으며, 세부 범위와 SLA는 후속 확정이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/fa8192b5c83d510ea8900022ca875715fee7df3a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
+++ b/scenarios/S07_investment_dashboard/deliverables/지표정의_화면구성_시트.xlsx
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,6 +1194,56 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20260725-investment-dashboard-approval-execution</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:20:13.680+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>리서치 담당</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S07:B00001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 관련 산출물에 반영한 실행 결과를 기록하고, 범위·산식·데이터 계약·라이선스·SLA·컴플라이언스는 후속 승인 게이트에서 확정한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>투자 대시보드를 거시경제·개별 종목 패널로 분리하고 갱신 주기 정책 및 데이터 신선도 표시 요구사항을 반영했으며, 세부 주기와 데이터 범위는 확정 대기 중이다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>투자 대시보드 기능정의서; 지표 갱신 정책서; 데이터 요구사항 정의서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/923b77d8d775d7fb90042ffdf190ce45b3653dd6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
